--- a/artfynd/A 35063-2026 artfynd.xlsx
+++ b/artfynd/A 35063-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -879,6 +879,1582 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/80984830</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137404211</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91173</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>820298</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7471006</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404211</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137404225</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91173</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>819911</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7471111</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404225</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137404210</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92222</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>820298</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7471006</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404210</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137404215</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79521</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>820251</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7471065</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404215</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137404221</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79521</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>820160</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7471020</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404221</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137404209</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79545</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>820311</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7470974</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404209</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137404213</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78924</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>820262</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7471064</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404213</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137404208</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79278</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>820336</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7471011</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404208</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137404212</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78521</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>820262</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7471064</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404212</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137404220</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57221</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>820177</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7471061</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404220</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137404239</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57221</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>820046</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7470936</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Stjärtfjäder</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404239</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137404222</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58196</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>819905</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7471114</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404222</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137404218</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80111</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>820211</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7471133</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404218</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137404217</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79544</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>820227</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7471127</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404217</t>
         </is>
       </c>
     </row>
@@ -886,6 +2462,20 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35063-2026 artfynd.xlsx
+++ b/artfynd/A 35063-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137404211</v>
       </c>
       <c r="B4" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137404225</v>
       </c>
       <c r="B5" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137404210</v>
       </c>
       <c r="B6" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137404215</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137404221</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>137404209</v>
       </c>
       <c r="B9" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>137404213</v>
       </c>
       <c r="B10" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>137404208</v>
       </c>
       <c r="B11" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137404212</v>
       </c>
       <c r="B12" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>137404218</v>
       </c>
       <c r="B16" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>137404217</v>
       </c>
       <c r="B17" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35063-2026 artfynd.xlsx
+++ b/artfynd/A 35063-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137404211</v>
       </c>
       <c r="B4" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137404225</v>
       </c>
       <c r="B5" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137404210</v>
       </c>
       <c r="B6" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137404215</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137404221</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>137404209</v>
       </c>
       <c r="B9" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>137404213</v>
       </c>
       <c r="B10" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>137404208</v>
       </c>
       <c r="B11" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137404212</v>
       </c>
       <c r="B12" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>137404218</v>
       </c>
       <c r="B16" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>137404217</v>
       </c>
       <c r="B17" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35063-2026 artfynd.xlsx
+++ b/artfynd/A 35063-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137404211</v>
       </c>
       <c r="B4" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137404225</v>
       </c>
       <c r="B5" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137404210</v>
       </c>
       <c r="B6" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137404215</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137404221</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>137404209</v>
       </c>
       <c r="B9" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>137404213</v>
       </c>
       <c r="B10" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>137404208</v>
       </c>
       <c r="B11" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137404212</v>
       </c>
       <c r="B12" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>137404218</v>
       </c>
       <c r="B16" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>137404217</v>
       </c>
       <c r="B17" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35063-2026 artfynd.xlsx
+++ b/artfynd/A 35063-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137404211</v>
       </c>
       <c r="B4" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137404225</v>
       </c>
       <c r="B5" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137404210</v>
       </c>
       <c r="B6" t="n">
-        <v>92238</v>
+        <v>92242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137404215</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137404221</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>137404209</v>
       </c>
       <c r="B9" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>137404213</v>
       </c>
       <c r="B10" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>137404208</v>
       </c>
       <c r="B11" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137404212</v>
       </c>
       <c r="B12" t="n">
-        <v>78535</v>
+        <v>78539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>137404220</v>
       </c>
       <c r="B13" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>137404239</v>
       </c>
       <c r="B14" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>137404222</v>
       </c>
       <c r="B15" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>137404218</v>
       </c>
       <c r="B16" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>137404217</v>
       </c>
       <c r="B17" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
